--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.4256334111</v>
+        <v>298487.0049003611</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547408</v>
+        <v>3013503.893776014</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20373567.14494819</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4789054.529283858</v>
       </c>
     </row>
     <row r="11">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1211,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1296,16 +1296,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>23.55275130756091</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1557,19 +1557,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344404</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1642,16 +1642,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1676,19 +1676,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,16 +1794,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1840,22 +1840,22 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>12.35200489467393</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1958,25 +1958,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="U18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2010,10 +2010,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2034,16 +2034,16 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>22.02246762618612</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2052,13 +2052,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2071,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2083,13 +2083,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3.252730413754638</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2147,13 +2147,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>36.38377949013847</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2198,25 +2198,25 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>192.6676677056849</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2280,19 +2280,19 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2353,10 +2353,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
@@ -2365,16 +2365,16 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>220.1862512213238</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="24">
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9.678041610869542</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2438,22 +2438,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>147.6655966646496</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2523,13 +2523,13 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2554,16 +2554,16 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.79691042959408</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2599,13 +2599,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2636,16 +2636,16 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>79.2253966117713</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2669,25 +2669,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>192.8779791104384</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>44.30348359856706</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2785,16 +2785,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>78.68895450699577</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>11.72852275604597</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
@@ -2879,10 +2879,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
         <v>200.1647286948216</v>
@@ -2918,10 +2918,10 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3076,16 +3076,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>200.3360962888297</v>
       </c>
       <c r="W32" t="n">
-        <v>35.49211325806013</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3095,31 +3095,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>147.6955921724596</v>
+        <v>72.61088677903452</v>
       </c>
     </row>
     <row r="34">
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3319,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y35" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3383,22 +3383,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>29.79900896488251</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>189.3719999999999</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3435,10 +3435,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>22.03399177268428</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3493,28 +3493,28 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>17.56289348969293</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3547,10 +3547,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3578,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>140.7326816555635</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3620,22 +3620,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>106.4456941689889</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>130.4655268502615</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3727,19 +3727,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3787,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="W41" t="n">
-        <v>177.6197007854552</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
     <row r="42">
@@ -3812,25 +3812,25 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>72.96582450647328</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>27.32974305220725</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3863,10 +3863,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>92.93786803496215</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>66.67524177233588</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>40.41261550970962</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82000000000029</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56000000000029</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.30000000000028</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348996</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>100.8903465994384</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.62772033681216</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>48.3650940741859</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>22.10246781155963</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>100.8903465994381</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>48.36509407418561</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>22.10246781155935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>83.71717171717171</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>55.43434343434343</v>
+        <v>97.8833284203818</v>
       </c>
       <c r="G17" t="n">
-        <v>27.15151515151514</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>57.68</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M17" t="n">
-        <v>84.28</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>57.68</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M18" t="n">
-        <v>84.28</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="N18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="U18" t="n">
-        <v>83.71717171717171</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="V18" t="n">
-        <v>55.43434343434343</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="W18" t="n">
-        <v>27.15151515151514</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="T19" t="n">
-        <v>87.08848484848485</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U19" t="n">
-        <v>87.08848484848485</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="V19" t="n">
-        <v>87.08848484848485</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="W19" t="n">
-        <v>58.80565656565657</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="X19" t="n">
-        <v>30.52282828282829</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>509.4342731452067</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C20" t="n">
-        <v>265.9999297108633</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D20" t="n">
-        <v>22.56558627651984</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E20" t="n">
-        <v>22.56558627651984</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F20" t="n">
-        <v>22.56558627651984</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G20" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>752.8686165795501</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X20" t="n">
-        <v>752.8686165795501</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y20" t="n">
-        <v>509.4342731452067</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>380.1728640094453</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="C21" t="n">
-        <v>205.7198347283183</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="D21" t="n">
-        <v>56.785425067067</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="E21" t="n">
-        <v>56.785425067067</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="F21" t="n">
-        <v>56.785425067067</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="G21" t="n">
-        <v>56.785425067067</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H21" t="n">
-        <v>56.785425067067</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>304.1765223866491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="V21" t="n">
-        <v>964</v>
+        <v>327.2640844659515</v>
       </c>
       <c r="W21" t="n">
-        <v>964</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="X21" t="n">
-        <v>756.1484997944672</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="Y21" t="n">
-        <v>548.3882010295133</v>
+        <v>132.6502787026334</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T23" t="n">
-        <v>728.5590416377008</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U23" t="n">
-        <v>728.5590416377008</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="V23" t="n">
-        <v>485.1246982033574</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="W23" t="n">
-        <v>241.690354769014</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="X23" t="n">
-        <v>19.28</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.28</v>
+        <v>122.6530896684844</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>119.3554287497824</v>
+        <v>433.7223438482202</v>
       </c>
       <c r="C24" t="n">
-        <v>119.3554287497824</v>
+        <v>259.2693145670932</v>
       </c>
       <c r="D24" t="n">
-        <v>119.3554287497824</v>
+        <v>110.334904905842</v>
       </c>
       <c r="E24" t="n">
-        <v>119.3554287497824</v>
+        <v>110.334904905842</v>
       </c>
       <c r="F24" t="n">
-        <v>119.3554287497824</v>
+        <v>110.334904905842</v>
       </c>
       <c r="G24" t="n">
-        <v>119.3554287497824</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H24" t="n">
-        <v>109.5796291428435</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>144.6375600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>383.2275600578374</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N24" t="n">
-        <v>621.8175600578375</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O24" t="n">
-        <v>860.4075600578375</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T24" t="n">
-        <v>790.5826554506689</v>
+        <v>641.4826426131742</v>
       </c>
       <c r="U24" t="n">
-        <v>562.359037187058</v>
+        <v>641.4826426131742</v>
       </c>
       <c r="V24" t="n">
-        <v>327.2069289553153</v>
+        <v>641.4826426131742</v>
       </c>
       <c r="W24" t="n">
-        <v>327.2069289553153</v>
+        <v>641.4826426131742</v>
       </c>
       <c r="X24" t="n">
-        <v>119.3554287497824</v>
+        <v>641.4826426131742</v>
       </c>
       <c r="Y24" t="n">
-        <v>119.3554287497824</v>
+        <v>433.7223438482202</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>964</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C26" t="n">
-        <v>720.5656565656566</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D26" t="n">
-        <v>720.5656565656566</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E26" t="n">
-        <v>720.5656565656566</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F26" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="X26" t="n">
-        <v>964</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="Y26" t="n">
-        <v>964</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>248.9941954572403</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="C27" t="n">
-        <v>248.9941954572403</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="D27" t="n">
-        <v>100.0597857959891</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="E27" t="n">
-        <v>100.0597857959891</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="F27" t="n">
-        <v>100.0597857959891</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G27" t="n">
-        <v>100.0597857959891</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>100.0597857959891</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>487.8331058683492</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N27" t="n">
-        <v>656.0154414866706</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O27" t="n">
-        <v>894.6054414866707</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>660.6438759116518</v>
+        <v>769.2309139849408</v>
       </c>
       <c r="V27" t="n">
-        <v>660.6438759116518</v>
+        <v>534.0788057531981</v>
       </c>
       <c r="W27" t="n">
-        <v>417.2095324773084</v>
+        <v>534.0788057531981</v>
       </c>
       <c r="X27" t="n">
-        <v>417.2095324773084</v>
+        <v>326.2273055476653</v>
       </c>
       <c r="Y27" t="n">
-        <v>417.2095324773084</v>
+        <v>326.2273055476653</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>961.308225475175</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>874.2758585542716</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D29" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E29" t="n">
-        <v>477.1313131313132</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F29" t="n">
-        <v>233.6969696969697</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>283.2269536926799</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="C30" t="n">
-        <v>283.2269536926799</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="D30" t="n">
-        <v>283.2269536926799</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="E30" t="n">
-        <v>283.2269536926799</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F30" t="n">
-        <v>271.3799610098052</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G30" t="n">
-        <v>132.6491355924207</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>725.41</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T30" t="n">
-        <v>761.813405358766</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U30" t="n">
-        <v>761.813405358766</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="V30" t="n">
-        <v>526.6612971270233</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="W30" t="n">
-        <v>283.2269536926799</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="X30" t="n">
-        <v>283.2269536926799</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="Y30" t="n">
-        <v>283.2269536926799</v>
+        <v>588.4532163200711</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="E32" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>487.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>487.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>487.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>487.3940537960203</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="W32" t="n">
-        <v>451.5434343434343</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="X32" t="n">
-        <v>234.3717171717172</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>108.2537617956292</v>
+        <v>587.3567013424552</v>
       </c>
       <c r="C33" t="n">
-        <v>108.2537617956292</v>
+        <v>587.3567013424552</v>
       </c>
       <c r="D33" t="n">
-        <v>108.2537617956292</v>
+        <v>438.4222916812039</v>
       </c>
       <c r="E33" t="n">
-        <v>108.2537617956292</v>
+        <v>279.1848366757484</v>
       </c>
       <c r="F33" t="n">
-        <v>108.2537617956292</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="G33" t="n">
-        <v>108.2537617956292</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H33" t="n">
-        <v>108.2537617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M33" t="n">
-        <v>568.2575600578374</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N33" t="n">
-        <v>781.1075600578374</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O33" t="n">
-        <v>790.6054414866707</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T33" t="n">
-        <v>860</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U33" t="n">
-        <v>860</v>
+        <v>660.701031422288</v>
       </c>
       <c r="V33" t="n">
-        <v>642.8282828282828</v>
+        <v>660.701031422288</v>
       </c>
       <c r="W33" t="n">
-        <v>425.6565656565656</v>
+        <v>660.701031422288</v>
       </c>
       <c r="X33" t="n">
-        <v>425.6565656565656</v>
+        <v>660.701031422288</v>
       </c>
       <c r="Y33" t="n">
-        <v>276.4690988156973</v>
+        <v>587.3567013424552</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>668.7151515151515</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C35" t="n">
-        <v>668.7151515151515</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D35" t="n">
-        <v>668.7151515151515</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E35" t="n">
-        <v>668.7151515151515</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F35" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X35" t="n">
-        <v>849.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y35" t="n">
-        <v>668.7151515151515</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>38.80652238664919</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M36" t="n">
-        <v>251.6565223866492</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N36" t="n">
-        <v>464.5065223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O36" t="n">
-        <v>677.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="U36" t="n">
-        <v>642.8282828282828</v>
+        <v>705.7335281915883</v>
       </c>
       <c r="V36" t="n">
-        <v>425.6565656565656</v>
+        <v>470.5814199598456</v>
       </c>
       <c r="W36" t="n">
-        <v>208.4848484848484</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>39.69443618776046</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>148.9833604548096</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W37" t="n">
-        <v>61.9509935339062</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y37" t="n">
-        <v>61.9509935339062</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>481.353720044753</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C38" t="n">
-        <v>264.1820028730358</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D38" t="n">
-        <v>246.4417064188005</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E38" t="n">
-        <v>29.26998924708335</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F38" t="n">
-        <v>29.26998924708335</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G38" t="n">
-        <v>29.26998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H38" t="n">
-        <v>29.26998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>29.26998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>504.9505276501126</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>710.8050498573519</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>698.5254372164702</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V38" t="n">
-        <v>698.5254372164702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W38" t="n">
-        <v>698.5254372164702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X38" t="n">
-        <v>698.5254372164702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y38" t="n">
-        <v>481.353720044753</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>333.8072531756357</v>
+        <v>353.7257600495809</v>
       </c>
       <c r="C39" t="n">
-        <v>159.3542238945086</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="D39" t="n">
-        <v>159.3542238945086</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="E39" t="n">
-        <v>159.3542238945086</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L39" t="n">
-        <v>355.4075600578374</v>
+        <v>178.8501590306595</v>
       </c>
       <c r="M39" t="n">
-        <v>568.2575600578374</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N39" t="n">
-        <v>568.2575600578374</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O39" t="n">
-        <v>607.9619638733197</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>758.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S39" t="n">
-        <v>758.8304705528857</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T39" t="n">
-        <v>758.8304705528857</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U39" t="n">
-        <v>541.6587533811685</v>
+        <v>461.2466632505798</v>
       </c>
       <c r="V39" t="n">
-        <v>541.6587533811685</v>
+        <v>353.7257600495809</v>
       </c>
       <c r="W39" t="n">
-        <v>541.6587533811685</v>
+        <v>353.7257600495809</v>
       </c>
       <c r="X39" t="n">
-        <v>333.8072531756357</v>
+        <v>353.7257600495809</v>
       </c>
       <c r="Y39" t="n">
-        <v>333.8072531756357</v>
+        <v>353.7257600495809</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>148.9833604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>148.9833604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>148.9833604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>148.9833604548096</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T40" t="n">
-        <v>148.9833604548096</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U40" t="n">
-        <v>148.9833604548096</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>148.9833604548096</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="C41" t="n">
-        <v>17.04</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>300.1647985849684</v>
       </c>
       <c r="M41" t="n">
-        <v>511.0008574955809</v>
+        <v>511.4548195661379</v>
       </c>
       <c r="N41" t="n">
-        <v>702.8050498573519</v>
+        <v>717.3093417733771</v>
       </c>
       <c r="O41" t="n">
-        <v>852</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="W41" t="n">
-        <v>662.4945454545455</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="X41" t="n">
-        <v>662.4945454545455</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="Y41" t="n">
-        <v>447.3430303030303</v>
+        <v>448.2340696092722</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>320.5274402498554</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="C42" t="n">
-        <v>320.5274402498554</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="D42" t="n">
-        <v>320.5274402498554</v>
+        <v>489.1825805481781</v>
       </c>
       <c r="E42" t="n">
-        <v>246.8245872130137</v>
+        <v>329.9451255427226</v>
       </c>
       <c r="F42" t="n">
-        <v>246.8245872130137</v>
+        <v>183.4105675696075</v>
       </c>
       <c r="G42" t="n">
-        <v>108.0937617956292</v>
+        <v>44.67974215222304</v>
       </c>
       <c r="H42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="N42" t="n">
-        <v>564.1375600578374</v>
+        <v>459.7635558748512</v>
       </c>
       <c r="O42" t="n">
-        <v>775.0075600578374</v>
+        <v>671.0535768560208</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>750.8304705528857</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>750.8304705528857</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>750.8304705528857</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>535.6789554013706</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V42" t="n">
-        <v>320.5274402498554</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W42" t="n">
-        <v>320.5274402498554</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="X42" t="n">
-        <v>320.5274402498554</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="Y42" t="n">
-        <v>320.5274402498554</v>
+        <v>638.1169902094293</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="C43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="D43" t="n">
-        <v>717.4677095097293</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="E43" t="n">
-        <v>717.4677095097293</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="F43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="G43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="H43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="I43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="J43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="K43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="L43" t="n">
-        <v>744.7818345174422</v>
+        <v>746.4788889868139</v>
       </c>
       <c r="M43" t="n">
-        <v>783.9698727096644</v>
+        <v>785.6669271790361</v>
       </c>
       <c r="N43" t="n">
-        <v>827.6607233651007</v>
+        <v>829.3577778344724</v>
       </c>
       <c r="O43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Y43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
     </row>
     <row r="44">
@@ -8433,10 +8433,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
         <v>230.3462332272727</v>
@@ -8445,10 +8445,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>255.0477063711817</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8518,19 +8518,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>167.5457393939394</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,10 +8670,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>245.0393459944755</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
         <v>230.3462332272727</v>
@@ -8682,10 +8682,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,13 +8749,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>162.790933923854</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8767,7 +8767,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812386</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8913,16 +8913,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,13 +8986,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>162.790933923854</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
@@ -9004,7 +9004,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>262.2416917349371</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,16 +9223,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
-        <v>166.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>169.0027207907052</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O18" t="n">
         <v>142.5962444444444</v>
@@ -9241,7 +9241,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9460,22 +9460,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P21" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>369.031319612638</v>
       </c>
       <c r="P24" t="n">
-        <v>238.6132356387368</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>301.2228591725469</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>177.2597568922521</v>
       </c>
       <c r="Q27" t="n">
         <v>210.0772877358491</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10171,19 +10171,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>371.3183728223746</v>
+        <v>244.7225752110828</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
@@ -10332,10 +10332,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M32" t="n">
-        <v>437.0731727773048</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>152.1900640695285</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>160.3791498673986</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>437.0731727773048</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10818,7 +10818,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10885,19 +10885,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>173.111405903722</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>182.7017028439216</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11046,16 +11046,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
-        <v>423.1546720428242</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
-        <v>380.8001812627454</v>
+        <v>277.2978653650641</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11122,22 +11122,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833333</v>
+        <v>238.4548774837949</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>141.6490351202224</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22978,10 +22978,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>356.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>339.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
         <v>354.683041620683</v>
@@ -23044,10 +23044,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>346.830300678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>360.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -23069,19 +23069,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23154,16 +23154,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>138.6744211998787</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
         <v>86.16204325169439</v>
@@ -23227,19 +23227,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>395.924535096324</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23306,19 +23306,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23415,19 +23415,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948375</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23500,16 +23500,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>228.4448529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23534,19 +23534,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>149.8076989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>131.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>119.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
         <v>112.2354442364965</v>
@@ -23637,7 +23637,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>2.447248692439093</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,16 +23652,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S16" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T16" t="n">
         <v>227.9455894282815</v>
@@ -23698,22 +23698,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
-        <v>353.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>378.8760457417114</v>
+        <v>394.5240408470375</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>314.8124021157672</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23816,25 +23816,25 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>175.8634344455351</v>
       </c>
       <c r="U18" t="n">
-        <v>197.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>204.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>223.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>181.1105852034775</v>
+        <v>178.1829599431613</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23868,10 +23868,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I19" t="n">
-        <v>155.4504749272583</v>
+        <v>127.8604496669421</v>
       </c>
       <c r="J19" t="n">
-        <v>93.35918011667277</v>
+        <v>65.76915485635664</v>
       </c>
       <c r="K19" t="n">
         <v>22.26949182588285</v>
@@ -23892,16 +23892,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>58.57201799137825</v>
       </c>
       <c r="R19" t="n">
-        <v>177.2933913771695</v>
+        <v>154.8446320166601</v>
       </c>
       <c r="S19" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
-        <v>205.9231218020954</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
         <v>286.3190293564909</v>
@@ -23910,13 +23910,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>197.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>190.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="20">
@@ -23929,10 +23929,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D20" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>203.0173518716929</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>207.2231591566513</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -23977,7 +23977,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y20" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="21">
@@ -24005,13 +24005,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
@@ -24023,13 +24023,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>53.01285336127661</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24056,25 +24056,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>59.02731545523469</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24138,7 +24138,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24150,7 +24150,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366913</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>382.7338416634806</v>
+        <v>280.3956145707916</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
@@ -24211,10 +24211,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24223,16 +24223,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>149.5448494571452</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="24">
@@ -24245,10 +24245,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>157.6450804554009</v>
@@ -24260,13 +24260,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>102.5574026256269</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24296,22 +24296,22 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>52.49913203017204</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24381,13 +24381,13 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W25" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X25" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
         <v>218.5846533520948</v>
@@ -24403,7 +24403,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
         <v>354.683041620683</v>
@@ -24412,16 +24412,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>405.0791353121173</v>
+        <v>194.5906600982693</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -24457,13 +24457,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X26" t="n">
         <v>369.731100678469</v>
@@ -24485,7 +24485,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
         <v>157.6450804554009</v>
@@ -24494,16 +24494,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>10.17123623964378</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24527,25 +24527,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>33.06340297053637</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -24600,13 +24600,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786024</v>
       </c>
       <c r="S28" t="n">
         <v>224.0165980369723</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24643,16 +24643,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>203.029937515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24697,7 +24697,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>87.84422914287157</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -24728,7 +24728,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>133.3406896373379</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24737,10 +24737,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24767,7 +24767,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -24776,10 +24776,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
@@ -24886,7 +24886,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
         <v>415.302737515135</v>
@@ -24898,7 +24898,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24919,13 +24919,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
         <v>223.0958495641314</v>
@@ -24934,16 +24934,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>127.4161621813053</v>
       </c>
       <c r="W32" t="n">
-        <v>313.7488554593529</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
-        <v>154.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24953,31 +24953,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>57.98710360484475</v>
+        <v>133.0718089982698</v>
       </c>
     </row>
     <row r="34">
@@ -25080,7 +25080,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180149</v>
       </c>
       <c r="S34" t="n">
         <v>224.0165980369723</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>153.3360307512229</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>382.7338416634806</v>
+        <v>170.4484560200385</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25123,13 +25123,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>191.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G35" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>124.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25177,10 +25177,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y35" t="n">
-        <v>206.8566378705984</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25241,22 +25241,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>141.8841621389553</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>16.40098520347755</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25293,10 +25293,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J37" t="n">
-        <v>71.32518834398849</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25311,10 +25311,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
         <v>177.2933913771695</v>
@@ -25335,7 +25335,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366916</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25351,28 +25351,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>150.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>337.1201481309901</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,10 +25393,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
@@ -25405,10 +25405,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25436,10 +25436,10 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>4.336530737820311</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25478,22 +25478,22 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>126.3548929804363</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
         <v>205.6826957773044</v>
@@ -25548,7 +25548,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
         <v>86.16204325169439</v>
@@ -25557,7 +25557,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
@@ -25569,7 +25569,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>156.0574714863295</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25585,19 +25585,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>152.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25645,16 +25645,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>327.7522584701349</v>
+        <v>139.7681670759793</v>
       </c>
       <c r="W41" t="n">
-        <v>171.6212679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>173.2379386560536</v>
+        <v>172.8136750387107</v>
       </c>
     </row>
     <row r="42">
@@ -25670,25 +25670,25 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>84.67925594892766</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>84.90570118428921</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
@@ -25721,10 +25721,10 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>12.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
         <v>251.6949831609196</v>
@@ -25749,13 +25749,13 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D43" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E43" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F43" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756325</v>
       </c>
       <c r="G43" t="n">
         <v>167.9909793584588</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405007</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405005</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405007</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060302</v>
+        <v>351669.2246312145</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245365</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245362</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845365</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845364</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.4228264389</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="C2" t="n">
         <v>48378.33248915087</v>
       </c>
       <c r="D2" t="n">
-        <v>51690.99534204105</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204107</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.6233062447</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909962</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411187</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411185</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411187</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411186</v>
+        <v>71833.19353176962</v>
       </c>
       <c r="P2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="E4" t="n">
-        <v>22.53282218066301</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>2099.754014286062</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1832752112465</v>
+        <v>2278.927672807631</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>3297.970381927695</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2099.754014286062</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>12650.97847486482</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>12650.97847486482</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860384</v>
+        <v>12650.97847486482</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.6625198604</v>
+        <v>46278.57847486482</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986038</v>
+        <v>46278.57847486482</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912105</v>
+        <v>40367.2100241361</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215243</v>
+        <v>-913.271144244005</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021525</v>
+        <v>56670.51599808772</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021526</v>
+        <v>56670.51599808768</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021526</v>
+        <v>56670.51599808769</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.37112779102</v>
+        <v>56670.51599808769</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779099</v>
+        <v>56670.51599808768</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779102</v>
+        <v>56670.51599808768</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991221</v>
+        <v>55559.02792190748</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>46278.57847486482</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,10 +35088,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35100,10 +35100,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35173,19 +35173,19 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35337,10 +35337,10 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,13 +35404,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -35422,7 +35422,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26.00000000000029</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35568,16 +35568,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,13 +35641,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -35659,7 +35659,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,16 +35878,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -35896,7 +35896,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36045,7 +36045,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N20" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O20" t="n">
         <v>150.7019698410586</v>
@@ -36115,22 +36115,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="P24" t="n">
-        <v>104.6388282244066</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>169.8811470892136</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="Q27" t="n">
         <v>70.09551364982758</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36826,19 +36826,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>239.9766607390412</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -36990,7 +36990,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>206.726939550032</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>9.59381962508408</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>21.82477008752444</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37464,7 +37464,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>206.726939550032</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37473,7 +37473,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37540,19 +37540,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>34.55702612384782</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>40.10545839947712</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37701,16 +37701,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
-        <v>193.7416084462334</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
-        <v>150.7019698410586</v>
+        <v>47.19965394337734</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37777,22 +37777,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>107.1131654004615</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>7.674627705892183</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
